--- a/Automated_Pipeline/REPORTS/Indicator_Weights_Summary.xlsx
+++ b/Automated_Pipeline/REPORTS/Indicator_Weights_Summary.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,10 +447,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Weight_Source</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Composite_Scored</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Source_CSV</t>
         </is>
@@ -472,12 +477,13 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>GOV Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -499,12 +505,13 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>GOV Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -526,12 +533,13 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>GOV Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -553,12 +561,13 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>GOV Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -580,12 +589,13 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>GOV Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -613,10 +623,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>GOV Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -644,10 +659,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>GOV Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -675,10 +695,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>GOV Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -706,10 +731,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>GOV Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -737,10 +767,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>GOV Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -768,10 +803,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>GOV Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -799,10 +839,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>GOV Theme 3 - Socioeconomic Vulnerability.csv</t>
         </is>
@@ -830,10 +875,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>GOV Theme 3 - Socioeconomic Vulnerability.csv</t>
         </is>
@@ -861,10 +911,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>GOV Theme 3 - Socioeconomic Vulnerability.csv</t>
         </is>
@@ -892,10 +947,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>GOV Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -923,10 +983,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>GOV Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -954,10 +1019,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>GOV Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -985,10 +1055,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>GOV Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -1016,10 +1091,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>GOV Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -1047,10 +1127,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>GOV Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -1078,10 +1163,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>GOV Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -1109,10 +1199,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>GOV Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -1140,10 +1235,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>GOV Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -1165,12 +1265,13 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>GOV Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -1192,12 +1293,13 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>GOV Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -1219,12 +1321,13 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>GOV Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -1246,12 +1349,13 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>GOV Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -1273,12 +1377,13 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>GOV Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -1306,10 +1411,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>GOV Theme 6 - Climate and Environmental Risk.csv</t>
         </is>
@@ -1337,10 +1447,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>GOV Theme 6 - Climate and Environmental Risk.csv</t>
         </is>
@@ -1368,10 +1483,15 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>GOV Theme 6 - Climate and Environmental Risk.csv</t>
         </is>
@@ -1399,10 +1519,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>GOV Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -1430,10 +1555,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>GOV Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -1461,10 +1591,15 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>GOV Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -1492,10 +1627,15 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>GOV Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -1523,10 +1663,15 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>GOV Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -1554,10 +1699,15 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>GOV Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -1585,10 +1735,15 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>GOV Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -1616,10 +1771,15 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>GOV Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -1647,10 +1807,15 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>GOV Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -1678,10 +1843,15 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>GOV Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -1709,10 +1879,15 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>GOV Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -1740,10 +1915,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>GOV Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -1771,10 +1951,15 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>GOV Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -1802,10 +1987,15 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>GOV Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -1833,10 +2023,15 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>GOV Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -1864,10 +2059,15 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>GOV Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -1884,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1915,10 +2115,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Weight_Source</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Composite_Scored</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Source_CSV</t>
         </is>
@@ -1940,12 +2145,13 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>DIS Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -1967,12 +2173,13 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>DIS Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -1994,12 +2201,13 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>DIS Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -2021,12 +2229,13 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>DIS Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -2048,12 +2257,13 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>DIS Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -2081,10 +2291,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>DIS Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -2112,10 +2327,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>DIS Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -2143,10 +2363,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>DIS Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -2174,10 +2399,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>DIS Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -2205,10 +2435,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>DIS Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -2236,10 +2471,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>DIS Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -2267,10 +2507,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>DIS Theme 3 - Socioeconomic Vulnerability.csv</t>
         </is>
@@ -2298,10 +2543,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>DIS Theme 3 - Socioeconomic Vulnerability.csv</t>
         </is>
@@ -2329,10 +2579,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>DIS Theme 3 - Socioeconomic Vulnerability.csv</t>
         </is>
@@ -2360,10 +2615,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2391,10 +2651,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2422,10 +2687,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2453,10 +2723,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2484,10 +2759,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2515,10 +2795,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2546,10 +2831,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2577,10 +2867,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2608,10 +2903,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2639,10 +2939,15 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2670,10 +2975,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2701,10 +3011,15 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2732,10 +3047,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2763,10 +3083,15 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2794,10 +3119,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2825,10 +3155,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>DIS Theme 4 - Service &amp; Infrastructure Vulnerability.csv</t>
         </is>
@@ -2850,12 +3185,13 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>DIS Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -2877,12 +3213,13 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>DIS Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -2904,12 +3241,13 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>DIS Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -2931,12 +3269,13 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>DIS Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -2958,12 +3297,13 @@
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>DIS Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -2991,10 +3331,15 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>DIS Theme 6 - Climate Change and Environmental Risk.csv</t>
         </is>
@@ -3022,10 +3367,15 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>DIS Theme 6 - Climate Change and Environmental Risk.csv</t>
         </is>
@@ -3053,10 +3403,15 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>DIS Theme 6 - Climate Change and Environmental Risk.csv</t>
         </is>
@@ -3084,10 +3439,15 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3115,10 +3475,15 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3146,10 +3511,15 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3177,10 +3547,15 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3208,10 +3583,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3239,10 +3619,15 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3270,10 +3655,15 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3301,10 +3691,15 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3332,10 +3727,15 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3363,10 +3763,15 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3394,10 +3799,15 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3425,10 +3835,15 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>DIS Theme 7 - Political Vulnerability.csv</t>
         </is>
@@ -3456,10 +3871,15 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>DIS Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -3487,10 +3907,15 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>DIS Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -3518,10 +3943,15 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>DIS Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -3549,10 +3979,15 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>DIS Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -3580,10 +4015,15 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>DIS Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -3611,10 +4051,15 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>DIS Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -3642,10 +4087,15 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>DIS Theme 8 - Gender Based Vulnerabilities.csv</t>
         </is>
@@ -3662,7 +4112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3693,10 +4143,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Weight_Source</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Composite_Scored</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Source_CSV</t>
         </is>
@@ -3718,12 +4173,13 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>CAD Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -3745,12 +4201,13 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>CAD Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -3772,12 +4229,13 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>CAD Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -3799,12 +4257,13 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>CAD Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -3826,12 +4285,13 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>CAD Theme 1 - Displacement Pressure.csv</t>
         </is>
@@ -3859,10 +4319,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>CAD Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -3890,10 +4355,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>CAD Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -3921,10 +4391,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>CAD Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -3952,10 +4427,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>CAD Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -3983,10 +4463,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>CAD Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -4014,10 +4499,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>CAD Theme 2 - Tensions and Conflict Risk.csv</t>
         </is>
@@ -4045,10 +4535,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>CAD Theme 3 - Socioeconomic Vulnerability.csv</t>
         </is>
@@ -4076,10 +4571,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>CAD Theme 3 - Socioeconomic Vulnerability.csv</t>
         </is>
@@ -4107,10 +4607,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>CAD Theme 3 - Socioeconomic Vulnerability.csv</t>
         </is>
@@ -4132,12 +4637,13 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>CAD Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -4159,12 +4665,13 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>CAD Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -4186,12 +4693,13 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>CAD Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -4213,12 +4721,13 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>CAD Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -4240,12 +4749,13 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>CAD Theme 5 - Demographic Tension Stress.csv</t>
         </is>
@@ -4273,10 +4783,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>CAD Theme 6 - Climate Change and Environmental Risk.csv</t>
         </is>
@@ -4304,10 +4819,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>CAD Theme 6 - Climate Change and Environmental Risk.csv</t>
         </is>
@@ -4335,10 +4855,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>kendall</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>CAD Theme 6 - Climate Change and Environmental Risk.csv</t>
         </is>
